--- a/DB_Design.xlsx
+++ b/DB_Design.xlsx
@@ -1,11 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30516"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D69EABDF-ECA3-4E9D-A79A-D2C1E58555E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vinnakota.rishik\Downloads\stage\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8AB2B1D-DD84-465D-BD57-0FD443DAF006}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="6" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="integration" sheetId="1" r:id="rId1"/>
@@ -18,10 +23,10 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">integration!$A$1:$G$39</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">metadata!$A$1:$G$110</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">rules!$A$1:$G$56</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">metadata!$A$1:$G$112</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">output!$A$1:$G$34</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">Relationships!$A$1:$F$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">rules!$A$1:$G$56</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -44,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1162" uniqueCount="431">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1168" uniqueCount="434">
   <si>
     <t>Table</t>
   </si>
@@ -1337,13 +1342,22 @@
   </si>
   <si>
     <t>integration: 4 | metadata: 5 | rules: 3 | output: 2 | users: 3 = 17 tables total.</t>
+  </si>
+  <si>
+    <t>container_name</t>
+  </si>
+  <si>
+    <t>safe region or quarantine or staging</t>
+  </si>
+  <si>
+    <t>we can store the data in the specified location to host it</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1369,6 +1383,17 @@
     <font>
       <sz val="10"/>
       <name val="Consolas"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="6">
@@ -1427,7 +1452,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1472,6 +1497,12 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1777,7 +1808,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G39"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="24" style="1" customWidth="1"/>
     <col min="2" max="2" width="26" customWidth="1"/>
@@ -1788,7 +1819,7 @@
     <col min="7" max="7" width="50" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="1" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1811,7 +1842,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A2" s="3" t="s">
         <v>7</v>
       </c>
@@ -1834,7 +1865,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A3" s="5"/>
       <c r="B3" s="4" t="s">
         <v>14</v>
@@ -1855,7 +1886,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A4" s="6"/>
       <c r="B4" s="7" t="s">
         <v>19</v>
@@ -1876,7 +1907,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A5" s="5"/>
       <c r="B5" s="4" t="s">
         <v>24</v>
@@ -1897,7 +1928,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A6" s="6"/>
       <c r="B6" s="7" t="s">
         <v>28</v>
@@ -1918,7 +1949,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A7" s="5"/>
       <c r="B7" s="4" t="s">
         <v>32</v>
@@ -1939,7 +1970,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A8" s="6"/>
       <c r="B8" s="7" t="s">
         <v>36</v>
@@ -1960,7 +1991,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A9" s="5"/>
       <c r="B9" s="4" t="s">
         <v>39</v>
@@ -1981,7 +2012,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A10" s="6"/>
       <c r="B10" s="7" t="s">
         <v>43</v>
@@ -2002,7 +2033,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A11" s="5"/>
       <c r="B11" s="5"/>
       <c r="C11" s="5"/>
@@ -2011,7 +2042,7 @@
       <c r="F11" s="5"/>
       <c r="G11" s="5"/>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A12" s="3" t="s">
         <v>45</v>
       </c>
@@ -2034,7 +2065,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A13" s="5"/>
       <c r="B13" s="4" t="s">
         <v>49</v>
@@ -2055,7 +2086,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A14" s="6"/>
       <c r="B14" s="7" t="s">
         <v>53</v>
@@ -2076,7 +2107,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A15" s="5"/>
       <c r="B15" s="4" t="s">
         <v>57</v>
@@ -2097,7 +2128,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A16" s="5"/>
       <c r="B16" s="5"/>
       <c r="C16" s="5"/>
@@ -2106,7 +2137,7 @@
       <c r="F16" s="5"/>
       <c r="G16" s="5"/>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A17" s="3" t="s">
         <v>60</v>
       </c>
@@ -2129,7 +2160,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A18" s="5"/>
       <c r="B18" s="4" t="s">
         <v>49</v>
@@ -2150,7 +2181,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A19" s="6"/>
       <c r="B19" s="7" t="s">
         <v>53</v>
@@ -2171,7 +2202,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A20" s="5"/>
       <c r="B20" s="4" t="s">
         <v>57</v>
@@ -2192,7 +2223,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A21" s="5"/>
       <c r="B21" s="5"/>
       <c r="C21" s="5"/>
@@ -2201,7 +2232,7 @@
       <c r="F21" s="5"/>
       <c r="G21" s="5"/>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A22" s="3" t="s">
         <v>65</v>
       </c>
@@ -2224,7 +2255,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A23" s="5"/>
       <c r="B23" s="4" t="s">
         <v>67</v>
@@ -2245,7 +2276,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="24" spans="1:7">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A24" s="6"/>
       <c r="B24" s="7" t="s">
         <v>71</v>
@@ -2266,7 +2297,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="25" spans="1:7">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A25" s="5"/>
       <c r="B25" s="4" t="s">
         <v>74</v>
@@ -2287,7 +2318,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A26" s="6"/>
       <c r="B26" s="7" t="s">
         <v>57</v>
@@ -2308,7 +2339,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="27" spans="1:7">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A27" s="5"/>
       <c r="B27" s="5"/>
       <c r="C27" s="5"/>
@@ -2317,7 +2348,7 @@
       <c r="F27" s="5"/>
       <c r="G27" s="5"/>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A28" s="5"/>
       <c r="B28" s="5"/>
       <c r="C28" s="5"/>
@@ -2326,7 +2357,7 @@
       <c r="F28" s="5"/>
       <c r="G28" s="5"/>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A29" s="5"/>
       <c r="B29" s="5"/>
       <c r="C29" s="5"/>
@@ -2335,7 +2366,7 @@
       <c r="F29" s="5"/>
       <c r="G29" s="5"/>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A30" s="5"/>
       <c r="B30" s="5"/>
       <c r="C30" s="5"/>
@@ -2344,7 +2375,7 @@
       <c r="F30" s="5"/>
       <c r="G30" s="5"/>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A31" s="5"/>
       <c r="B31" s="5"/>
       <c r="C31" s="5"/>
@@ -2353,7 +2384,7 @@
       <c r="F31" s="5"/>
       <c r="G31" s="5"/>
     </row>
-    <row r="32" spans="1:7">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A32" s="5"/>
       <c r="B32" s="5"/>
       <c r="C32" s="5"/>
@@ -2362,7 +2393,7 @@
       <c r="F32" s="5"/>
       <c r="G32" s="5"/>
     </row>
-    <row r="33" spans="1:7">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A33" s="5"/>
       <c r="B33" s="5"/>
       <c r="C33" s="5"/>
@@ -2371,7 +2402,7 @@
       <c r="F33" s="5"/>
       <c r="G33" s="5"/>
     </row>
-    <row r="34" spans="1:7">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A34" s="5"/>
       <c r="B34" s="5"/>
       <c r="C34" s="5"/>
@@ -2380,7 +2411,7 @@
       <c r="F34" s="5"/>
       <c r="G34" s="5"/>
     </row>
-    <row r="35" spans="1:7">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A35" s="5"/>
       <c r="B35" s="5"/>
       <c r="C35" s="5"/>
@@ -2389,7 +2420,7 @@
       <c r="F35" s="5"/>
       <c r="G35" s="5"/>
     </row>
-    <row r="36" spans="1:7">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A36" s="5"/>
       <c r="B36" s="5"/>
       <c r="C36" s="5"/>
@@ -2398,7 +2429,7 @@
       <c r="F36" s="5"/>
       <c r="G36" s="5"/>
     </row>
-    <row r="37" spans="1:7">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A37" s="5"/>
       <c r="B37" s="5"/>
       <c r="C37" s="5"/>
@@ -2407,7 +2438,7 @@
       <c r="F37" s="5"/>
       <c r="G37" s="5"/>
     </row>
-    <row r="38" spans="1:7">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A38" s="5"/>
       <c r="B38" s="5"/>
       <c r="C38" s="5"/>
@@ -2416,7 +2447,7 @@
       <c r="F38" s="5"/>
       <c r="G38" s="5"/>
     </row>
-    <row r="39" spans="1:7">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A39" s="5"/>
       <c r="B39" s="5"/>
       <c r="C39" s="5"/>
@@ -2433,8 +2464,8 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:G158"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <dimension ref="A1:G160"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="24" style="1" customWidth="1"/>
     <col min="2" max="2" width="26" customWidth="1"/>
@@ -2445,7 +2476,7 @@
     <col min="7" max="7" width="50" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="1" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2468,7 +2499,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A2" s="3" t="s">
         <v>79</v>
       </c>
@@ -2491,7 +2522,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A3" s="5"/>
       <c r="B3" s="4" t="s">
         <v>8</v>
@@ -2512,12 +2543,12 @@
         <v>84</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A4" s="6"/>
       <c r="B4" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="17" t="s">
         <v>15</v>
       </c>
       <c r="D4" s="6" t="s">
@@ -2533,7 +2564,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A5" s="5"/>
       <c r="B5" s="4" t="s">
         <v>86</v>
@@ -2554,7 +2585,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A6" s="6"/>
       <c r="B6" s="7" t="s">
         <v>89</v>
@@ -2575,7 +2606,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A7" s="5"/>
       <c r="B7" s="4" t="s">
         <v>92</v>
@@ -2596,7 +2627,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A8" s="6"/>
       <c r="B8" s="7" t="s">
         <v>95</v>
@@ -2617,7 +2648,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A9" s="5"/>
       <c r="B9" s="4" t="s">
         <v>99</v>
@@ -2638,7 +2669,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A10" s="6"/>
       <c r="B10" s="7" t="s">
         <v>103</v>
@@ -2659,7 +2690,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A11" s="5"/>
       <c r="B11" s="4" t="s">
         <v>39</v>
@@ -2680,7 +2711,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A12" s="6"/>
       <c r="B12" s="7" t="s">
         <v>43</v>
@@ -2691,7 +2722,7 @@
       <c r="D12" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="E12" s="6" t="s">
+      <c r="E12" s="17" t="s">
         <v>11</v>
       </c>
       <c r="F12" s="6" t="s">
@@ -2701,108 +2732,96 @@
         <v>108</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
-      <c r="A13" s="5"/>
-      <c r="B13" s="5"/>
-      <c r="C13" s="5"/>
-      <c r="D13" s="5"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="5"/>
-      <c r="G13" s="5"/>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14" s="3" t="s">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A13" s="6"/>
+      <c r="B13" s="7"/>
+      <c r="C13" s="6"/>
+      <c r="D13" s="6"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="6"/>
+      <c r="G13" s="6"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A14" s="6"/>
+      <c r="B14" s="16" t="s">
+        <v>431</v>
+      </c>
+      <c r="C14" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D14" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="E14" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F14" s="17" t="s">
+        <v>432</v>
+      </c>
+      <c r="G14" s="6" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A15" s="5"/>
+      <c r="B15" s="5"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A16" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B16" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C16" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="D16" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="E14" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F14" s="5" t="s">
+      <c r="E16" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F16" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="G14" s="5" t="s">
+      <c r="G16" s="5" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
-      <c r="A15" s="5"/>
-      <c r="B15" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="F15" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="G15" s="5" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16" s="6"/>
-      <c r="B16" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E16" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="F16" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="G16" s="6" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A17" s="5"/>
       <c r="B17" s="4" t="s">
-        <v>119</v>
+        <v>80</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>54</v>
+        <v>9</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>21</v>
+        <v>83</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>11</v>
+        <v>114</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>120</v>
+        <v>81</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A18" s="6"/>
       <c r="B18" s="7" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>25</v>
+        <v>68</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>21</v>
@@ -2811,19 +2830,19 @@
         <v>11</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>96</v>
+        <v>117</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A19" s="5"/>
       <c r="B19" s="4" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>104</v>
+        <v>54</v>
       </c>
       <c r="D19" s="5" t="s">
         <v>21</v>
@@ -2832,37 +2851,37 @@
         <v>11</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A20" s="6"/>
       <c r="B20" s="7" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>25</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>75</v>
+        <v>21</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>11</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>128</v>
+        <v>96</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A21" s="5"/>
       <c r="B21" s="4" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>104</v>
@@ -2874,111 +2893,111 @@
         <v>11</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>105</v>
+        <v>125</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A22" s="6"/>
       <c r="B22" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F22" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="G22" s="6" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A23" s="5"/>
+      <c r="B23" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="G23" s="5" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A24" s="6"/>
+      <c r="B24" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="C22" s="6" t="s">
+      <c r="C24" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="D22" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E22" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="F22" s="6" t="s">
+      <c r="D24" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F24" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="G22" s="6" t="s">
+      <c r="G24" s="6" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
-      <c r="A23" s="5"/>
-      <c r="B23" s="5"/>
-      <c r="C23" s="5"/>
-      <c r="D23" s="5"/>
-      <c r="E23" s="5"/>
-      <c r="F23" s="5"/>
-      <c r="G23" s="5"/>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24" s="3" t="s">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A25" s="5"/>
+      <c r="B25" s="5"/>
+      <c r="C25" s="5"/>
+      <c r="D25" s="5"/>
+      <c r="E25" s="5"/>
+      <c r="F25" s="5"/>
+      <c r="G25" s="5"/>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A26" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="B24" s="4" t="s">
+      <c r="B26" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="C24" s="5" t="s">
+      <c r="C26" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="D24" s="5" t="s">
+      <c r="D26" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="E24" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F24" s="5" t="s">
+      <c r="E26" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F26" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="G24" s="5" t="s">
+      <c r="G26" s="5" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="25" spans="1:7">
-      <c r="A25" s="5"/>
-      <c r="B25" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D25" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="E25" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="F25" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G25" s="5" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26" s="6"/>
-      <c r="B26" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="C26" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D26" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E26" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="F26" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="G26" s="6" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A27" s="5"/>
       <c r="B27" s="4" t="s">
-        <v>138</v>
+        <v>8</v>
       </c>
       <c r="C27" s="5" t="s">
         <v>9</v>
@@ -2987,19 +3006,19 @@
         <v>83</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>139</v>
+        <v>47</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>140</v>
+        <v>12</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A28" s="6"/>
       <c r="B28" s="7" t="s">
-        <v>142</v>
+        <v>57</v>
       </c>
       <c r="C28" s="6" t="s">
         <v>15</v>
@@ -3008,177 +3027,177 @@
         <v>21</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>11</v>
+        <v>114</v>
       </c>
       <c r="F28" s="6" t="s">
-        <v>37</v>
+        <v>58</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A29" s="5"/>
       <c r="B29" s="4" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>21</v>
+        <v>83</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>11</v>
+        <v>139</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A30" s="6"/>
       <c r="B30" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E30" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F30" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="G30" s="6" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A31" s="5"/>
+      <c r="B31" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E31" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F31" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="G31" s="5" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A32" s="6"/>
+      <c r="B32" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="C30" s="6" t="s">
+      <c r="C32" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="D30" s="6" t="s">
+      <c r="D32" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="E30" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="F30" s="6" t="s">
+      <c r="E32" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F32" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="G30" s="6" t="s">
+      <c r="G32" s="6" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="31" spans="1:7">
-      <c r="A31" s="5"/>
-      <c r="B31" s="5"/>
-      <c r="C31" s="5"/>
-      <c r="D31" s="5"/>
-      <c r="E31" s="5"/>
-      <c r="F31" s="5"/>
-      <c r="G31" s="5"/>
-    </row>
-    <row r="32" spans="1:7">
-      <c r="A32" s="3" t="s">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A33" s="5"/>
+      <c r="B33" s="5"/>
+      <c r="C33" s="5"/>
+      <c r="D33" s="5"/>
+      <c r="E33" s="5"/>
+      <c r="F33" s="5"/>
+      <c r="G33" s="5"/>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A34" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="B32" s="4" t="s">
+      <c r="B34" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="C32" s="5" t="s">
+      <c r="C34" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="D32" s="5" t="s">
+      <c r="D34" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="E32" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F32" s="5" t="s">
+      <c r="E34" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F34" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="G32" s="5" t="s">
+      <c r="G34" s="5" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="33" spans="1:7">
-      <c r="A33" s="5"/>
-      <c r="B33" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C33" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D33" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="E33" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="F33" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G33" s="5" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7">
-      <c r="A34" s="6"/>
-      <c r="B34" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="C34" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D34" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E34" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="F34" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="G34" s="6" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A35" s="5"/>
       <c r="B35" s="4" t="s">
-        <v>86</v>
+        <v>8</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>21</v>
+        <v>83</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>11</v>
+        <v>47</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>154</v>
+        <v>12</v>
       </c>
       <c r="G35" s="5" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A36" s="6"/>
       <c r="B36" s="7" t="s">
-        <v>138</v>
+        <v>57</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>83</v>
+        <v>21</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>139</v>
+        <v>114</v>
       </c>
       <c r="F36" s="6" t="s">
-        <v>140</v>
+        <v>58</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A37" s="5"/>
       <c r="B37" s="4" t="s">
-        <v>142</v>
+        <v>86</v>
       </c>
       <c r="C37" s="5" t="s">
         <v>15</v>
@@ -3187,180 +3206,180 @@
         <v>21</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>11</v>
+        <v>114</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>37</v>
+        <v>154</v>
       </c>
       <c r="G37" s="5" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A38" s="6"/>
       <c r="B38" s="7" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>21</v>
+        <v>83</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>11</v>
+        <v>139</v>
       </c>
       <c r="F38" s="6" t="s">
-        <v>156</v>
+        <v>140</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A39" s="5"/>
       <c r="B39" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D39" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E39" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F39" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="G39" s="5" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A40" s="6"/>
+      <c r="B40" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="C40" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D40" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E40" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F40" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="G40" s="6" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A41" s="5"/>
+      <c r="B41" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="C39" s="5" t="s">
+      <c r="C41" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="D39" s="5" t="s">
+      <c r="D41" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="E39" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F39" s="5" t="s">
+      <c r="E41" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F41" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="G39" s="5" t="s">
+      <c r="G41" s="5" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="40" spans="1:7">
-      <c r="A40" s="5"/>
-      <c r="B40" s="5"/>
-      <c r="C40" s="5"/>
-      <c r="D40" s="5"/>
-      <c r="E40" s="5"/>
-      <c r="F40" s="5"/>
-      <c r="G40" s="5"/>
-    </row>
-    <row r="41" spans="1:7">
-      <c r="A41" s="3" t="s">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A42" s="5"/>
+      <c r="B42" s="5"/>
+      <c r="C42" s="5"/>
+      <c r="D42" s="5"/>
+      <c r="E42" s="5"/>
+      <c r="F42" s="5"/>
+      <c r="G42" s="5"/>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A43" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="B41" s="4" t="s">
+      <c r="B43" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="C41" s="5" t="s">
+      <c r="C43" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D41" s="5" t="s">
+      <c r="D43" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="E41" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F41" s="5" t="s">
+      <c r="E43" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F43" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="G41" s="5" t="s">
+      <c r="G43" s="5" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="42" spans="1:7">
-      <c r="A42" s="5"/>
-      <c r="B42" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C42" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D42" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="E42" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="F42" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G42" s="5" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7">
-      <c r="A43" s="6"/>
-      <c r="B43" s="7" t="s">
-        <v>162</v>
-      </c>
-      <c r="C43" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="D43" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E43" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="F43" s="6" t="s">
-        <v>163</v>
-      </c>
-      <c r="G43" s="6" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A44" s="5"/>
       <c r="B44" s="4" t="s">
-        <v>165</v>
+        <v>8</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>21</v>
+        <v>83</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>11</v>
+        <v>47</v>
       </c>
       <c r="F44" s="5" t="s">
-        <v>107</v>
+        <v>12</v>
       </c>
       <c r="G44" s="5" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A45" s="6"/>
       <c r="B45" s="7" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>75</v>
+        <v>21</v>
       </c>
       <c r="E45" s="6" t="s">
         <v>11</v>
       </c>
       <c r="F45" s="6" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="G45" s="6" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A46" s="5"/>
       <c r="B46" s="4" t="s">
-        <v>32</v>
+        <v>165</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="D46" s="5" t="s">
         <v>21</v>
@@ -3369,19 +3388,19 @@
         <v>11</v>
       </c>
       <c r="F46" s="5" t="s">
-        <v>170</v>
+        <v>107</v>
       </c>
       <c r="G46" s="5" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A47" s="6"/>
       <c r="B47" s="7" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="D47" s="6" t="s">
         <v>75</v>
@@ -3390,40 +3409,40 @@
         <v>11</v>
       </c>
       <c r="F47" s="6" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="G47" s="6" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A48" s="5"/>
       <c r="B48" s="4" t="s">
-        <v>175</v>
+        <v>32</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>75</v>
+        <v>21</v>
       </c>
       <c r="E48" s="5" t="s">
         <v>11</v>
       </c>
       <c r="F48" s="5" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="G48" s="5" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A49" s="6"/>
       <c r="B49" s="7" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>100</v>
+        <v>54</v>
       </c>
       <c r="D49" s="6" t="s">
         <v>75</v>
@@ -3432,31 +3451,55 @@
         <v>11</v>
       </c>
       <c r="F49" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="G49" s="6" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A50" s="5"/>
+      <c r="B50" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="C50" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="D50" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="G49" s="6" t="s">
+      <c r="E50" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F50" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="G50" s="5" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A51" s="6"/>
+      <c r="B51" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="C51" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="D51" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="E51" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F51" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="G51" s="6" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="50" spans="1:7">
-      <c r="A50" s="5"/>
-      <c r="B50" s="5"/>
-      <c r="C50" s="5"/>
-      <c r="D50" s="5"/>
-      <c r="E50" s="5"/>
-      <c r="F50" s="5"/>
-      <c r="G50" s="5"/>
-    </row>
-    <row r="51" spans="1:7">
-      <c r="A51" s="5"/>
-      <c r="B51" s="5"/>
-      <c r="C51" s="5"/>
-      <c r="D51" s="5"/>
-      <c r="E51" s="5"/>
-      <c r="F51" s="5"/>
-      <c r="G51" s="5"/>
-    </row>
-    <row r="52" spans="1:7">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A52" s="5"/>
       <c r="B52" s="5"/>
       <c r="C52" s="5"/>
@@ -3465,7 +3508,7 @@
       <c r="F52" s="5"/>
       <c r="G52" s="5"/>
     </row>
-    <row r="53" spans="1:7">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A53" s="5"/>
       <c r="B53" s="5"/>
       <c r="C53" s="5"/>
@@ -3474,7 +3517,7 @@
       <c r="F53" s="5"/>
       <c r="G53" s="5"/>
     </row>
-    <row r="54" spans="1:7">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A54" s="5"/>
       <c r="B54" s="5"/>
       <c r="C54" s="5"/>
@@ -3483,7 +3526,7 @@
       <c r="F54" s="5"/>
       <c r="G54" s="5"/>
     </row>
-    <row r="55" spans="1:7">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A55" s="5"/>
       <c r="B55" s="5"/>
       <c r="C55" s="5"/>
@@ -3492,7 +3535,7 @@
       <c r="F55" s="5"/>
       <c r="G55" s="5"/>
     </row>
-    <row r="56" spans="1:7">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A56" s="5"/>
       <c r="B56" s="5"/>
       <c r="C56" s="5"/>
@@ -3501,7 +3544,7 @@
       <c r="F56" s="5"/>
       <c r="G56" s="5"/>
     </row>
-    <row r="57" spans="1:7">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A57" s="5"/>
       <c r="B57" s="5"/>
       <c r="C57" s="5"/>
@@ -3510,7 +3553,7 @@
       <c r="F57" s="5"/>
       <c r="G57" s="5"/>
     </row>
-    <row r="58" spans="1:7">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A58" s="5"/>
       <c r="B58" s="5"/>
       <c r="C58" s="5"/>
@@ -3519,7 +3562,7 @@
       <c r="F58" s="5"/>
       <c r="G58" s="5"/>
     </row>
-    <row r="59" spans="1:7">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A59" s="5"/>
       <c r="B59" s="5"/>
       <c r="C59" s="5"/>
@@ -3528,7 +3571,7 @@
       <c r="F59" s="5"/>
       <c r="G59" s="5"/>
     </row>
-    <row r="60" spans="1:7">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A60" s="5"/>
       <c r="B60" s="5"/>
       <c r="C60" s="5"/>
@@ -3537,7 +3580,7 @@
       <c r="F60" s="5"/>
       <c r="G60" s="5"/>
     </row>
-    <row r="61" spans="1:7">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A61" s="5"/>
       <c r="B61" s="5"/>
       <c r="C61" s="5"/>
@@ -3546,7 +3589,7 @@
       <c r="F61" s="5"/>
       <c r="G61" s="5"/>
     </row>
-    <row r="62" spans="1:7">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A62" s="5"/>
       <c r="B62" s="5"/>
       <c r="C62" s="5"/>
@@ -3555,7 +3598,7 @@
       <c r="F62" s="5"/>
       <c r="G62" s="5"/>
     </row>
-    <row r="63" spans="1:7">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A63" s="5"/>
       <c r="B63" s="5"/>
       <c r="C63" s="5"/>
@@ -3564,7 +3607,7 @@
       <c r="F63" s="5"/>
       <c r="G63" s="5"/>
     </row>
-    <row r="64" spans="1:7">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A64" s="5"/>
       <c r="B64" s="5"/>
       <c r="C64" s="5"/>
@@ -3573,7 +3616,7 @@
       <c r="F64" s="5"/>
       <c r="G64" s="5"/>
     </row>
-    <row r="65" spans="1:7">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A65" s="5"/>
       <c r="B65" s="5"/>
       <c r="C65" s="5"/>
@@ -3582,7 +3625,7 @@
       <c r="F65" s="5"/>
       <c r="G65" s="5"/>
     </row>
-    <row r="66" spans="1:7">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A66" s="5"/>
       <c r="B66" s="5"/>
       <c r="C66" s="5"/>
@@ -3591,7 +3634,7 @@
       <c r="F66" s="5"/>
       <c r="G66" s="5"/>
     </row>
-    <row r="67" spans="1:7">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A67" s="5"/>
       <c r="B67" s="5"/>
       <c r="C67" s="5"/>
@@ -3600,7 +3643,7 @@
       <c r="F67" s="5"/>
       <c r="G67" s="5"/>
     </row>
-    <row r="68" spans="1:7">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A68" s="5"/>
       <c r="B68" s="5"/>
       <c r="C68" s="5"/>
@@ -3609,7 +3652,7 @@
       <c r="F68" s="5"/>
       <c r="G68" s="5"/>
     </row>
-    <row r="69" spans="1:7">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A69" s="5"/>
       <c r="B69" s="5"/>
       <c r="C69" s="5"/>
@@ -3618,7 +3661,7 @@
       <c r="F69" s="5"/>
       <c r="G69" s="5"/>
     </row>
-    <row r="70" spans="1:7">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A70" s="5"/>
       <c r="B70" s="5"/>
       <c r="C70" s="5"/>
@@ -3627,7 +3670,7 @@
       <c r="F70" s="5"/>
       <c r="G70" s="5"/>
     </row>
-    <row r="71" spans="1:7">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A71" s="5"/>
       <c r="B71" s="5"/>
       <c r="C71" s="5"/>
@@ -3636,7 +3679,7 @@
       <c r="F71" s="5"/>
       <c r="G71" s="5"/>
     </row>
-    <row r="72" spans="1:7">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A72" s="5"/>
       <c r="B72" s="5"/>
       <c r="C72" s="5"/>
@@ -3645,7 +3688,7 @@
       <c r="F72" s="5"/>
       <c r="G72" s="5"/>
     </row>
-    <row r="73" spans="1:7">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A73" s="5"/>
       <c r="B73" s="5"/>
       <c r="C73" s="5"/>
@@ -3654,7 +3697,7 @@
       <c r="F73" s="5"/>
       <c r="G73" s="5"/>
     </row>
-    <row r="74" spans="1:7">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A74" s="5"/>
       <c r="B74" s="5"/>
       <c r="C74" s="5"/>
@@ -3663,7 +3706,7 @@
       <c r="F74" s="5"/>
       <c r="G74" s="5"/>
     </row>
-    <row r="75" spans="1:7">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A75" s="5"/>
       <c r="B75" s="5"/>
       <c r="C75" s="5"/>
@@ -3672,7 +3715,7 @@
       <c r="F75" s="5"/>
       <c r="G75" s="5"/>
     </row>
-    <row r="76" spans="1:7">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A76" s="5"/>
       <c r="B76" s="5"/>
       <c r="C76" s="5"/>
@@ -3681,7 +3724,7 @@
       <c r="F76" s="5"/>
       <c r="G76" s="5"/>
     </row>
-    <row r="77" spans="1:7">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A77" s="5"/>
       <c r="B77" s="5"/>
       <c r="C77" s="5"/>
@@ -3690,7 +3733,7 @@
       <c r="F77" s="5"/>
       <c r="G77" s="5"/>
     </row>
-    <row r="78" spans="1:7">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A78" s="5"/>
       <c r="B78" s="5"/>
       <c r="C78" s="5"/>
@@ -3699,7 +3742,7 @@
       <c r="F78" s="5"/>
       <c r="G78" s="5"/>
     </row>
-    <row r="79" spans="1:7">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A79" s="5"/>
       <c r="B79" s="5"/>
       <c r="C79" s="5"/>
@@ -3708,7 +3751,7 @@
       <c r="F79" s="5"/>
       <c r="G79" s="5"/>
     </row>
-    <row r="80" spans="1:7">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A80" s="5"/>
       <c r="B80" s="5"/>
       <c r="C80" s="5"/>
@@ -3717,7 +3760,7 @@
       <c r="F80" s="5"/>
       <c r="G80" s="5"/>
     </row>
-    <row r="81" spans="1:7">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A81" s="5"/>
       <c r="B81" s="5"/>
       <c r="C81" s="5"/>
@@ -3726,7 +3769,7 @@
       <c r="F81" s="5"/>
       <c r="G81" s="5"/>
     </row>
-    <row r="82" spans="1:7">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A82" s="5"/>
       <c r="B82" s="5"/>
       <c r="C82" s="5"/>
@@ -3735,7 +3778,7 @@
       <c r="F82" s="5"/>
       <c r="G82" s="5"/>
     </row>
-    <row r="83" spans="1:7">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A83" s="5"/>
       <c r="B83" s="5"/>
       <c r="C83" s="5"/>
@@ -3744,7 +3787,7 @@
       <c r="F83" s="5"/>
       <c r="G83" s="5"/>
     </row>
-    <row r="84" spans="1:7">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A84" s="5"/>
       <c r="B84" s="5"/>
       <c r="C84" s="5"/>
@@ -3753,7 +3796,7 @@
       <c r="F84" s="5"/>
       <c r="G84" s="5"/>
     </row>
-    <row r="85" spans="1:7">
+    <row r="85" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A85" s="5"/>
       <c r="B85" s="5"/>
       <c r="C85" s="5"/>
@@ -3762,7 +3805,7 @@
       <c r="F85" s="5"/>
       <c r="G85" s="5"/>
     </row>
-    <row r="86" spans="1:7">
+    <row r="86" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A86" s="5"/>
       <c r="B86" s="5"/>
       <c r="C86" s="5"/>
@@ -3771,7 +3814,7 @@
       <c r="F86" s="5"/>
       <c r="G86" s="5"/>
     </row>
-    <row r="87" spans="1:7">
+    <row r="87" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A87" s="5"/>
       <c r="B87" s="5"/>
       <c r="C87" s="5"/>
@@ -3780,7 +3823,7 @@
       <c r="F87" s="5"/>
       <c r="G87" s="5"/>
     </row>
-    <row r="88" spans="1:7">
+    <row r="88" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A88" s="5"/>
       <c r="B88" s="5"/>
       <c r="C88" s="5"/>
@@ -3789,7 +3832,7 @@
       <c r="F88" s="5"/>
       <c r="G88" s="5"/>
     </row>
-    <row r="89" spans="1:7">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A89" s="5"/>
       <c r="B89" s="5"/>
       <c r="C89" s="5"/>
@@ -3798,7 +3841,7 @@
       <c r="F89" s="5"/>
       <c r="G89" s="5"/>
     </row>
-    <row r="90" spans="1:7">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A90" s="5"/>
       <c r="B90" s="5"/>
       <c r="C90" s="5"/>
@@ -3807,7 +3850,7 @@
       <c r="F90" s="5"/>
       <c r="G90" s="5"/>
     </row>
-    <row r="91" spans="1:7">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A91" s="5"/>
       <c r="B91" s="5"/>
       <c r="C91" s="5"/>
@@ -3816,7 +3859,7 @@
       <c r="F91" s="5"/>
       <c r="G91" s="5"/>
     </row>
-    <row r="92" spans="1:7">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A92" s="5"/>
       <c r="B92" s="5"/>
       <c r="C92" s="5"/>
@@ -3825,7 +3868,7 @@
       <c r="F92" s="5"/>
       <c r="G92" s="5"/>
     </row>
-    <row r="93" spans="1:7">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A93" s="5"/>
       <c r="B93" s="5"/>
       <c r="C93" s="5"/>
@@ -3834,7 +3877,7 @@
       <c r="F93" s="5"/>
       <c r="G93" s="5"/>
     </row>
-    <row r="94" spans="1:7">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A94" s="5"/>
       <c r="B94" s="5"/>
       <c r="C94" s="5"/>
@@ -3843,7 +3886,7 @@
       <c r="F94" s="5"/>
       <c r="G94" s="5"/>
     </row>
-    <row r="95" spans="1:7">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A95" s="5"/>
       <c r="B95" s="5"/>
       <c r="C95" s="5"/>
@@ -3852,7 +3895,7 @@
       <c r="F95" s="5"/>
       <c r="G95" s="5"/>
     </row>
-    <row r="96" spans="1:7">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A96" s="5"/>
       <c r="B96" s="5"/>
       <c r="C96" s="5"/>
@@ -3861,7 +3904,7 @@
       <c r="F96" s="5"/>
       <c r="G96" s="5"/>
     </row>
-    <row r="97" spans="1:7">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A97" s="5"/>
       <c r="B97" s="5"/>
       <c r="C97" s="5"/>
@@ -3870,7 +3913,7 @@
       <c r="F97" s="5"/>
       <c r="G97" s="5"/>
     </row>
-    <row r="98" spans="1:7">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A98" s="5"/>
       <c r="B98" s="5"/>
       <c r="C98" s="5"/>
@@ -3879,7 +3922,7 @@
       <c r="F98" s="5"/>
       <c r="G98" s="5"/>
     </row>
-    <row r="99" spans="1:7">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A99" s="5"/>
       <c r="B99" s="5"/>
       <c r="C99" s="5"/>
@@ -3888,7 +3931,7 @@
       <c r="F99" s="5"/>
       <c r="G99" s="5"/>
     </row>
-    <row r="100" spans="1:7">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A100" s="5"/>
       <c r="B100" s="5"/>
       <c r="C100" s="5"/>
@@ -3897,7 +3940,7 @@
       <c r="F100" s="5"/>
       <c r="G100" s="5"/>
     </row>
-    <row r="101" spans="1:7">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A101" s="5"/>
       <c r="B101" s="5"/>
       <c r="C101" s="5"/>
@@ -3906,7 +3949,7 @@
       <c r="F101" s="5"/>
       <c r="G101" s="5"/>
     </row>
-    <row r="102" spans="1:7">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A102" s="5"/>
       <c r="B102" s="5"/>
       <c r="C102" s="5"/>
@@ -3915,7 +3958,7 @@
       <c r="F102" s="5"/>
       <c r="G102" s="5"/>
     </row>
-    <row r="103" spans="1:7">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A103" s="5"/>
       <c r="B103" s="5"/>
       <c r="C103" s="5"/>
@@ -3924,7 +3967,7 @@
       <c r="F103" s="5"/>
       <c r="G103" s="5"/>
     </row>
-    <row r="104" spans="1:7">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A104" s="5"/>
       <c r="B104" s="5"/>
       <c r="C104" s="5"/>
@@ -3933,7 +3976,7 @@
       <c r="F104" s="5"/>
       <c r="G104" s="5"/>
     </row>
-    <row r="105" spans="1:7">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A105" s="5"/>
       <c r="B105" s="5"/>
       <c r="C105" s="5"/>
@@ -3942,7 +3985,7 @@
       <c r="F105" s="5"/>
       <c r="G105" s="5"/>
     </row>
-    <row r="106" spans="1:7">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A106" s="5"/>
       <c r="B106" s="5"/>
       <c r="C106" s="5"/>
@@ -3951,7 +3994,7 @@
       <c r="F106" s="5"/>
       <c r="G106" s="5"/>
     </row>
-    <row r="107" spans="1:7">
+    <row r="107" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A107" s="5"/>
       <c r="B107" s="5"/>
       <c r="C107" s="5"/>
@@ -3960,7 +4003,7 @@
       <c r="F107" s="5"/>
       <c r="G107" s="5"/>
     </row>
-    <row r="108" spans="1:7">
+    <row r="108" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A108" s="5"/>
       <c r="B108" s="5"/>
       <c r="C108" s="5"/>
@@ -3969,7 +4012,7 @@
       <c r="F108" s="5"/>
       <c r="G108" s="5"/>
     </row>
-    <row r="109" spans="1:7">
+    <row r="109" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A109" s="5"/>
       <c r="B109" s="5"/>
       <c r="C109" s="5"/>
@@ -3978,7 +4021,7 @@
       <c r="F109" s="5"/>
       <c r="G109" s="5"/>
     </row>
-    <row r="110" spans="1:7">
+    <row r="110" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A110" s="5"/>
       <c r="B110" s="5"/>
       <c r="C110" s="5"/>
@@ -3987,7 +4030,7 @@
       <c r="F110" s="5"/>
       <c r="G110" s="5"/>
     </row>
-    <row r="111" spans="1:7">
+    <row r="111" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A111" s="5"/>
       <c r="B111" s="5"/>
       <c r="C111" s="5"/>
@@ -3996,7 +4039,7 @@
       <c r="F111" s="5"/>
       <c r="G111" s="5"/>
     </row>
-    <row r="112" spans="1:7">
+    <row r="112" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A112" s="5"/>
       <c r="B112" s="5"/>
       <c r="C112" s="5"/>
@@ -4005,7 +4048,7 @@
       <c r="F112" s="5"/>
       <c r="G112" s="5"/>
     </row>
-    <row r="113" spans="1:7">
+    <row r="113" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A113" s="5"/>
       <c r="B113" s="5"/>
       <c r="C113" s="5"/>
@@ -4014,7 +4057,7 @@
       <c r="F113" s="5"/>
       <c r="G113" s="5"/>
     </row>
-    <row r="114" spans="1:7">
+    <row r="114" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A114" s="5"/>
       <c r="B114" s="5"/>
       <c r="C114" s="5"/>
@@ -4023,7 +4066,7 @@
       <c r="F114" s="5"/>
       <c r="G114" s="5"/>
     </row>
-    <row r="115" spans="1:7">
+    <row r="115" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A115" s="5"/>
       <c r="B115" s="5"/>
       <c r="C115" s="5"/>
@@ -4032,7 +4075,7 @@
       <c r="F115" s="5"/>
       <c r="G115" s="5"/>
     </row>
-    <row r="116" spans="1:7">
+    <row r="116" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A116" s="5"/>
       <c r="B116" s="5"/>
       <c r="C116" s="5"/>
@@ -4041,7 +4084,7 @@
       <c r="F116" s="5"/>
       <c r="G116" s="5"/>
     </row>
-    <row r="117" spans="1:7">
+    <row r="117" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A117" s="5"/>
       <c r="B117" s="5"/>
       <c r="C117" s="5"/>
@@ -4050,7 +4093,7 @@
       <c r="F117" s="5"/>
       <c r="G117" s="5"/>
     </row>
-    <row r="118" spans="1:7">
+    <row r="118" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A118" s="5"/>
       <c r="B118" s="5"/>
       <c r="C118" s="5"/>
@@ -4059,7 +4102,7 @@
       <c r="F118" s="5"/>
       <c r="G118" s="5"/>
     </row>
-    <row r="119" spans="1:7">
+    <row r="119" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A119" s="5"/>
       <c r="B119" s="5"/>
       <c r="C119" s="5"/>
@@ -4068,7 +4111,7 @@
       <c r="F119" s="5"/>
       <c r="G119" s="5"/>
     </row>
-    <row r="120" spans="1:7">
+    <row r="120" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A120" s="5"/>
       <c r="B120" s="5"/>
       <c r="C120" s="5"/>
@@ -4077,7 +4120,7 @@
       <c r="F120" s="5"/>
       <c r="G120" s="5"/>
     </row>
-    <row r="121" spans="1:7">
+    <row r="121" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A121" s="5"/>
       <c r="B121" s="5"/>
       <c r="C121" s="5"/>
@@ -4086,7 +4129,7 @@
       <c r="F121" s="5"/>
       <c r="G121" s="5"/>
     </row>
-    <row r="122" spans="1:7">
+    <row r="122" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A122" s="5"/>
       <c r="B122" s="5"/>
       <c r="C122" s="5"/>
@@ -4095,7 +4138,7 @@
       <c r="F122" s="5"/>
       <c r="G122" s="5"/>
     </row>
-    <row r="123" spans="1:7">
+    <row r="123" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A123" s="5"/>
       <c r="B123" s="5"/>
       <c r="C123" s="5"/>
@@ -4104,7 +4147,7 @@
       <c r="F123" s="5"/>
       <c r="G123" s="5"/>
     </row>
-    <row r="124" spans="1:7">
+    <row r="124" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A124" s="5"/>
       <c r="B124" s="5"/>
       <c r="C124" s="5"/>
@@ -4113,7 +4156,7 @@
       <c r="F124" s="5"/>
       <c r="G124" s="5"/>
     </row>
-    <row r="125" spans="1:7">
+    <row r="125" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A125" s="5"/>
       <c r="B125" s="5"/>
       <c r="C125" s="5"/>
@@ -4122,7 +4165,7 @@
       <c r="F125" s="5"/>
       <c r="G125" s="5"/>
     </row>
-    <row r="126" spans="1:7">
+    <row r="126" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A126" s="5"/>
       <c r="B126" s="5"/>
       <c r="C126" s="5"/>
@@ -4131,7 +4174,7 @@
       <c r="F126" s="5"/>
       <c r="G126" s="5"/>
     </row>
-    <row r="127" spans="1:7">
+    <row r="127" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A127" s="5"/>
       <c r="B127" s="5"/>
       <c r="C127" s="5"/>
@@ -4140,7 +4183,7 @@
       <c r="F127" s="5"/>
       <c r="G127" s="5"/>
     </row>
-    <row r="128" spans="1:7">
+    <row r="128" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A128" s="5"/>
       <c r="B128" s="5"/>
       <c r="C128" s="5"/>
@@ -4149,7 +4192,7 @@
       <c r="F128" s="5"/>
       <c r="G128" s="5"/>
     </row>
-    <row r="129" spans="1:7">
+    <row r="129" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A129" s="5"/>
       <c r="B129" s="5"/>
       <c r="C129" s="5"/>
@@ -4158,7 +4201,7 @@
       <c r="F129" s="5"/>
       <c r="G129" s="5"/>
     </row>
-    <row r="130" spans="1:7">
+    <row r="130" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A130" s="5"/>
       <c r="B130" s="5"/>
       <c r="C130" s="5"/>
@@ -4167,7 +4210,7 @@
       <c r="F130" s="5"/>
       <c r="G130" s="5"/>
     </row>
-    <row r="131" spans="1:7">
+    <row r="131" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A131" s="5"/>
       <c r="B131" s="5"/>
       <c r="C131" s="5"/>
@@ -4176,7 +4219,7 @@
       <c r="F131" s="5"/>
       <c r="G131" s="5"/>
     </row>
-    <row r="132" spans="1:7">
+    <row r="132" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A132" s="5"/>
       <c r="B132" s="5"/>
       <c r="C132" s="5"/>
@@ -4185,7 +4228,7 @@
       <c r="F132" s="5"/>
       <c r="G132" s="5"/>
     </row>
-    <row r="133" spans="1:7">
+    <row r="133" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A133" s="5"/>
       <c r="B133" s="5"/>
       <c r="C133" s="5"/>
@@ -4194,7 +4237,7 @@
       <c r="F133" s="5"/>
       <c r="G133" s="5"/>
     </row>
-    <row r="134" spans="1:7">
+    <row r="134" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A134" s="5"/>
       <c r="B134" s="5"/>
       <c r="C134" s="5"/>
@@ -4203,7 +4246,7 @@
       <c r="F134" s="5"/>
       <c r="G134" s="5"/>
     </row>
-    <row r="135" spans="1:7">
+    <row r="135" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A135" s="5"/>
       <c r="B135" s="5"/>
       <c r="C135" s="5"/>
@@ -4212,7 +4255,7 @@
       <c r="F135" s="5"/>
       <c r="G135" s="5"/>
     </row>
-    <row r="136" spans="1:7">
+    <row r="136" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A136" s="5"/>
       <c r="B136" s="5"/>
       <c r="C136" s="5"/>
@@ -4221,7 +4264,7 @@
       <c r="F136" s="5"/>
       <c r="G136" s="5"/>
     </row>
-    <row r="137" spans="1:7">
+    <row r="137" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A137" s="5"/>
       <c r="B137" s="5"/>
       <c r="C137" s="5"/>
@@ -4230,7 +4273,7 @@
       <c r="F137" s="5"/>
       <c r="G137" s="5"/>
     </row>
-    <row r="138" spans="1:7">
+    <row r="138" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A138" s="5"/>
       <c r="B138" s="5"/>
       <c r="C138" s="5"/>
@@ -4239,7 +4282,7 @@
       <c r="F138" s="5"/>
       <c r="G138" s="5"/>
     </row>
-    <row r="139" spans="1:7">
+    <row r="139" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A139" s="5"/>
       <c r="B139" s="5"/>
       <c r="C139" s="5"/>
@@ -4248,7 +4291,7 @@
       <c r="F139" s="5"/>
       <c r="G139" s="5"/>
     </row>
-    <row r="140" spans="1:7">
+    <row r="140" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A140" s="5"/>
       <c r="B140" s="5"/>
       <c r="C140" s="5"/>
@@ -4257,7 +4300,7 @@
       <c r="F140" s="5"/>
       <c r="G140" s="5"/>
     </row>
-    <row r="141" spans="1:7">
+    <row r="141" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A141" s="5"/>
       <c r="B141" s="5"/>
       <c r="C141" s="5"/>
@@ -4266,7 +4309,7 @@
       <c r="F141" s="5"/>
       <c r="G141" s="5"/>
     </row>
-    <row r="142" spans="1:7">
+    <row r="142" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A142" s="5"/>
       <c r="B142" s="5"/>
       <c r="C142" s="5"/>
@@ -4275,7 +4318,7 @@
       <c r="F142" s="5"/>
       <c r="G142" s="5"/>
     </row>
-    <row r="143" spans="1:7">
+    <row r="143" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A143" s="5"/>
       <c r="B143" s="5"/>
       <c r="C143" s="5"/>
@@ -4284,7 +4327,7 @@
       <c r="F143" s="5"/>
       <c r="G143" s="5"/>
     </row>
-    <row r="144" spans="1:7">
+    <row r="144" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A144" s="5"/>
       <c r="B144" s="5"/>
       <c r="C144" s="5"/>
@@ -4293,7 +4336,7 @@
       <c r="F144" s="5"/>
       <c r="G144" s="5"/>
     </row>
-    <row r="145" spans="1:7">
+    <row r="145" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A145" s="5"/>
       <c r="B145" s="5"/>
       <c r="C145" s="5"/>
@@ -4302,7 +4345,7 @@
       <c r="F145" s="5"/>
       <c r="G145" s="5"/>
     </row>
-    <row r="146" spans="1:7">
+    <row r="146" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A146" s="5"/>
       <c r="B146" s="5"/>
       <c r="C146" s="5"/>
@@ -4311,7 +4354,7 @@
       <c r="F146" s="5"/>
       <c r="G146" s="5"/>
     </row>
-    <row r="147" spans="1:7">
+    <row r="147" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A147" s="5"/>
       <c r="B147" s="5"/>
       <c r="C147" s="5"/>
@@ -4320,7 +4363,7 @@
       <c r="F147" s="5"/>
       <c r="G147" s="5"/>
     </row>
-    <row r="148" spans="1:7">
+    <row r="148" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A148" s="5"/>
       <c r="B148" s="5"/>
       <c r="C148" s="5"/>
@@ -4329,7 +4372,7 @@
       <c r="F148" s="5"/>
       <c r="G148" s="5"/>
     </row>
-    <row r="149" spans="1:7">
+    <row r="149" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A149" s="5"/>
       <c r="B149" s="5"/>
       <c r="C149" s="5"/>
@@ -4338,7 +4381,7 @@
       <c r="F149" s="5"/>
       <c r="G149" s="5"/>
     </row>
-    <row r="150" spans="1:7">
+    <row r="150" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A150" s="5"/>
       <c r="B150" s="5"/>
       <c r="C150" s="5"/>
@@ -4347,7 +4390,7 @@
       <c r="F150" s="5"/>
       <c r="G150" s="5"/>
     </row>
-    <row r="151" spans="1:7">
+    <row r="151" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A151" s="5"/>
       <c r="B151" s="5"/>
       <c r="C151" s="5"/>
@@ -4356,7 +4399,7 @@
       <c r="F151" s="5"/>
       <c r="G151" s="5"/>
     </row>
-    <row r="152" spans="1:7">
+    <row r="152" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A152" s="5"/>
       <c r="B152" s="5"/>
       <c r="C152" s="5"/>
@@ -4365,7 +4408,7 @@
       <c r="F152" s="5"/>
       <c r="G152" s="5"/>
     </row>
-    <row r="153" spans="1:7">
+    <row r="153" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A153" s="5"/>
       <c r="B153" s="5"/>
       <c r="C153" s="5"/>
@@ -4374,7 +4417,7 @@
       <c r="F153" s="5"/>
       <c r="G153" s="5"/>
     </row>
-    <row r="154" spans="1:7">
+    <row r="154" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A154" s="5"/>
       <c r="B154" s="5"/>
       <c r="C154" s="5"/>
@@ -4383,7 +4426,7 @@
       <c r="F154" s="5"/>
       <c r="G154" s="5"/>
     </row>
-    <row r="155" spans="1:7">
+    <row r="155" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A155" s="5"/>
       <c r="B155" s="5"/>
       <c r="C155" s="5"/>
@@ -4392,7 +4435,7 @@
       <c r="F155" s="5"/>
       <c r="G155" s="5"/>
     </row>
-    <row r="156" spans="1:7">
+    <row r="156" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A156" s="5"/>
       <c r="B156" s="5"/>
       <c r="C156" s="5"/>
@@ -4401,7 +4444,7 @@
       <c r="F156" s="5"/>
       <c r="G156" s="5"/>
     </row>
-    <row r="157" spans="1:7">
+    <row r="157" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A157" s="5"/>
       <c r="B157" s="5"/>
       <c r="C157" s="5"/>
@@ -4410,7 +4453,7 @@
       <c r="F157" s="5"/>
       <c r="G157" s="5"/>
     </row>
-    <row r="158" spans="1:7">
+    <row r="158" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A158" s="5"/>
       <c r="B158" s="5"/>
       <c r="C158" s="5"/>
@@ -4419,8 +4462,26 @@
       <c r="F158" s="5"/>
       <c r="G158" s="5"/>
     </row>
+    <row r="159" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A159" s="5"/>
+      <c r="B159" s="5"/>
+      <c r="C159" s="5"/>
+      <c r="D159" s="5"/>
+      <c r="E159" s="5"/>
+      <c r="F159" s="5"/>
+      <c r="G159" s="5"/>
+    </row>
+    <row r="160" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A160" s="5"/>
+      <c r="B160" s="5"/>
+      <c r="C160" s="5"/>
+      <c r="D160" s="5"/>
+      <c r="E160" s="5"/>
+      <c r="F160" s="5"/>
+      <c r="G160" s="5"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G110" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
+  <autoFilter ref="A1:G112" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4428,7 +4489,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:G56"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="24" style="1" customWidth="1"/>
     <col min="2" max="2" width="26" customWidth="1"/>
@@ -4439,7 +4500,7 @@
     <col min="7" max="7" width="50" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="1" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -4462,7 +4523,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A2" s="3" t="s">
         <v>180</v>
       </c>
@@ -4485,7 +4546,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A3" s="5"/>
       <c r="B3" s="4" t="s">
         <v>184</v>
@@ -4506,7 +4567,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A4" s="6"/>
       <c r="B4" s="7" t="s">
         <v>187</v>
@@ -4527,7 +4588,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A5" s="5"/>
       <c r="B5" s="4" t="s">
         <v>190</v>
@@ -4548,7 +4609,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A6" s="6"/>
       <c r="B6" s="7" t="s">
         <v>193</v>
@@ -4569,7 +4630,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A7" s="5"/>
       <c r="B7" s="4" t="s">
         <v>99</v>
@@ -4590,7 +4651,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A8" s="6"/>
       <c r="B8" s="7" t="s">
         <v>103</v>
@@ -4611,7 +4672,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A9" s="5"/>
       <c r="B9" s="4" t="s">
         <v>199</v>
@@ -4632,7 +4693,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A10" s="6"/>
       <c r="B10" s="7" t="s">
         <v>39</v>
@@ -4653,7 +4714,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A11" s="5"/>
       <c r="B11" s="4" t="s">
         <v>43</v>
@@ -4674,7 +4735,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A12" s="5"/>
       <c r="B12" s="5"/>
       <c r="C12" s="5"/>
@@ -4683,7 +4744,7 @@
       <c r="F12" s="5"/>
       <c r="G12" s="5"/>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A13" s="3" t="s">
         <v>202</v>
       </c>
@@ -4706,7 +4767,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A14" s="5"/>
       <c r="B14" s="4" t="s">
         <v>181</v>
@@ -4727,7 +4788,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A15" s="6"/>
       <c r="B15" s="7" t="s">
         <v>208</v>
@@ -4748,7 +4809,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A16" s="5"/>
       <c r="B16" s="4" t="s">
         <v>210</v>
@@ -4769,7 +4830,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A17" s="6"/>
       <c r="B17" s="7" t="s">
         <v>213</v>
@@ -4790,7 +4851,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A18" s="5"/>
       <c r="B18" s="4" t="s">
         <v>217</v>
@@ -4811,7 +4872,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A19" s="6"/>
       <c r="B19" s="7" t="s">
         <v>220</v>
@@ -4832,7 +4893,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A20" s="5"/>
       <c r="B20" s="4" t="s">
         <v>223</v>
@@ -4853,7 +4914,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A21" s="6"/>
       <c r="B21" s="7" t="s">
         <v>36</v>
@@ -4874,7 +4935,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A22" s="5"/>
       <c r="B22" s="4" t="s">
         <v>39</v>
@@ -4895,7 +4956,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A23" s="5"/>
       <c r="B23" s="5"/>
       <c r="C23" s="5"/>
@@ -4904,7 +4965,7 @@
       <c r="F23" s="5"/>
       <c r="G23" s="5"/>
     </row>
-    <row r="24" spans="1:7">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A24" s="3" t="s">
         <v>226</v>
       </c>
@@ -4927,7 +4988,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="25" spans="1:7">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A25" s="5"/>
       <c r="B25" s="4" t="s">
         <v>80</v>
@@ -4948,7 +5009,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A26" s="6"/>
       <c r="B26" s="7" t="s">
         <v>110</v>
@@ -4969,7 +5030,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="27" spans="1:7">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A27" s="5"/>
       <c r="B27" s="4" t="s">
         <v>181</v>
@@ -4990,7 +5051,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A28" s="6"/>
       <c r="B28" s="7" t="s">
         <v>203</v>
@@ -5011,7 +5072,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A29" s="5"/>
       <c r="B29" s="4" t="s">
         <v>235</v>
@@ -5032,7 +5093,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A30" s="6"/>
       <c r="B30" s="7" t="s">
         <v>220</v>
@@ -5053,7 +5114,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A31" s="5"/>
       <c r="B31" s="4" t="s">
         <v>217</v>
@@ -5074,7 +5135,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="32" spans="1:7">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A32" s="6"/>
       <c r="B32" s="7" t="s">
         <v>213</v>
@@ -5095,7 +5156,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="33" spans="1:7">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A33" s="5"/>
       <c r="B33" s="4" t="s">
         <v>223</v>
@@ -5116,7 +5177,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="34" spans="1:7">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A34" s="6"/>
       <c r="B34" s="7" t="s">
         <v>36</v>
@@ -5137,7 +5198,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="35" spans="1:7">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A35" s="5"/>
       <c r="B35" s="4" t="s">
         <v>39</v>
@@ -5158,7 +5219,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="36" spans="1:7">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A36" s="6"/>
       <c r="B36" s="7" t="s">
         <v>43</v>
@@ -5179,7 +5240,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="37" spans="1:7">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A37" s="5"/>
       <c r="B37" s="5"/>
       <c r="C37" s="5"/>
@@ -5188,7 +5249,7 @@
       <c r="F37" s="5"/>
       <c r="G37" s="5"/>
     </row>
-    <row r="38" spans="1:7">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A38" s="5"/>
       <c r="B38" s="5"/>
       <c r="C38" s="5"/>
@@ -5197,7 +5258,7 @@
       <c r="F38" s="5"/>
       <c r="G38" s="5"/>
     </row>
-    <row r="39" spans="1:7">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A39" s="5"/>
       <c r="B39" s="5"/>
       <c r="C39" s="5"/>
@@ -5206,7 +5267,7 @@
       <c r="F39" s="5"/>
       <c r="G39" s="5"/>
     </row>
-    <row r="40" spans="1:7">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A40" s="5"/>
       <c r="B40" s="5"/>
       <c r="C40" s="5"/>
@@ -5215,7 +5276,7 @@
       <c r="F40" s="5"/>
       <c r="G40" s="5"/>
     </row>
-    <row r="41" spans="1:7">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A41" s="5"/>
       <c r="B41" s="5"/>
       <c r="C41" s="5"/>
@@ -5224,7 +5285,7 @@
       <c r="F41" s="5"/>
       <c r="G41" s="5"/>
     </row>
-    <row r="42" spans="1:7">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A42" s="5"/>
       <c r="B42" s="5"/>
       <c r="C42" s="5"/>
@@ -5233,7 +5294,7 @@
       <c r="F42" s="5"/>
       <c r="G42" s="5"/>
     </row>
-    <row r="43" spans="1:7">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A43" s="5"/>
       <c r="B43" s="5"/>
       <c r="C43" s="5"/>
@@ -5242,7 +5303,7 @@
       <c r="F43" s="5"/>
       <c r="G43" s="5"/>
     </row>
-    <row r="44" spans="1:7">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A44" s="5"/>
       <c r="B44" s="5"/>
       <c r="C44" s="5"/>
@@ -5251,7 +5312,7 @@
       <c r="F44" s="5"/>
       <c r="G44" s="5"/>
     </row>
-    <row r="45" spans="1:7">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A45" s="5"/>
       <c r="B45" s="5"/>
       <c r="C45" s="5"/>
@@ -5260,7 +5321,7 @@
       <c r="F45" s="5"/>
       <c r="G45" s="5"/>
     </row>
-    <row r="46" spans="1:7">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A46" s="5"/>
       <c r="B46" s="5"/>
       <c r="C46" s="5"/>
@@ -5269,7 +5330,7 @@
       <c r="F46" s="5"/>
       <c r="G46" s="5"/>
     </row>
-    <row r="47" spans="1:7">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A47" s="5"/>
       <c r="B47" s="5"/>
       <c r="C47" s="5"/>
@@ -5278,7 +5339,7 @@
       <c r="F47" s="5"/>
       <c r="G47" s="5"/>
     </row>
-    <row r="48" spans="1:7">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A48" s="5"/>
       <c r="B48" s="5"/>
       <c r="C48" s="5"/>
@@ -5287,7 +5348,7 @@
       <c r="F48" s="5"/>
       <c r="G48" s="5"/>
     </row>
-    <row r="49" spans="1:7">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A49" s="5"/>
       <c r="B49" s="5"/>
       <c r="C49" s="5"/>
@@ -5296,7 +5357,7 @@
       <c r="F49" s="5"/>
       <c r="G49" s="5"/>
     </row>
-    <row r="50" spans="1:7">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A50" s="5"/>
       <c r="B50" s="5"/>
       <c r="C50" s="5"/>
@@ -5305,7 +5366,7 @@
       <c r="F50" s="5"/>
       <c r="G50" s="5"/>
     </row>
-    <row r="51" spans="1:7">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A51" s="5"/>
       <c r="B51" s="5"/>
       <c r="C51" s="5"/>
@@ -5314,7 +5375,7 @@
       <c r="F51" s="5"/>
       <c r="G51" s="5"/>
     </row>
-    <row r="52" spans="1:7">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A52" s="5"/>
       <c r="B52" s="5"/>
       <c r="C52" s="5"/>
@@ -5323,7 +5384,7 @@
       <c r="F52" s="5"/>
       <c r="G52" s="5"/>
     </row>
-    <row r="53" spans="1:7">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A53" s="5"/>
       <c r="B53" s="5"/>
       <c r="C53" s="5"/>
@@ -5332,7 +5393,7 @@
       <c r="F53" s="5"/>
       <c r="G53" s="5"/>
     </row>
-    <row r="54" spans="1:7">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A54" s="5"/>
       <c r="B54" s="5"/>
       <c r="C54" s="5"/>
@@ -5341,7 +5402,7 @@
       <c r="F54" s="5"/>
       <c r="G54" s="5"/>
     </row>
-    <row r="55" spans="1:7">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A55" s="5"/>
       <c r="B55" s="5"/>
       <c r="C55" s="5"/>
@@ -5350,7 +5411,7 @@
       <c r="F55" s="5"/>
       <c r="G55" s="5"/>
     </row>
-    <row r="56" spans="1:7">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A56" s="5"/>
       <c r="B56" s="5"/>
       <c r="C56" s="5"/>
@@ -5368,7 +5429,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:G34"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="24" style="1" customWidth="1"/>
     <col min="2" max="2" width="26" customWidth="1"/>
@@ -5379,7 +5440,7 @@
     <col min="7" max="7" width="50" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="1" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -5402,7 +5463,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A2" s="3" t="s">
         <v>244</v>
       </c>
@@ -5425,7 +5486,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A3" s="5"/>
       <c r="B3" s="4" t="s">
         <v>248</v>
@@ -5446,7 +5507,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A4" s="6"/>
       <c r="B4" s="7" t="s">
         <v>32</v>
@@ -5467,7 +5528,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A5" s="5"/>
       <c r="B5" s="4" t="s">
         <v>162</v>
@@ -5488,7 +5549,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A6" s="6"/>
       <c r="B6" s="7" t="s">
         <v>165</v>
@@ -5509,7 +5570,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A7" s="5"/>
       <c r="B7" s="4" t="s">
         <v>167</v>
@@ -5530,7 +5591,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A8" s="6"/>
       <c r="B8" s="7" t="s">
         <v>258</v>
@@ -5551,7 +5612,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A9" s="5"/>
       <c r="B9" s="4" t="s">
         <v>261</v>
@@ -5572,7 +5633,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A10" s="6"/>
       <c r="B10" s="7" t="s">
         <v>263</v>
@@ -5593,7 +5654,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A11" s="5"/>
       <c r="B11" s="4" t="s">
         <v>266</v>
@@ -5614,7 +5675,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A12" s="6"/>
       <c r="B12" s="7" t="s">
         <v>178</v>
@@ -5635,7 +5696,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A13" s="5"/>
       <c r="B13" s="5"/>
       <c r="C13" s="5"/>
@@ -5644,7 +5705,7 @@
       <c r="F13" s="5"/>
       <c r="G13" s="5"/>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A14" s="3" t="s">
         <v>270</v>
       </c>
@@ -5667,7 +5728,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A15" s="5"/>
       <c r="B15" s="4" t="s">
         <v>245</v>
@@ -5688,7 +5749,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A16" s="6"/>
       <c r="B16" s="7" t="s">
         <v>80</v>
@@ -5709,7 +5770,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A17" s="5"/>
       <c r="B17" s="4" t="s">
         <v>110</v>
@@ -5730,7 +5791,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A18" s="6"/>
       <c r="B18" s="7" t="s">
         <v>227</v>
@@ -5751,7 +5812,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A19" s="5"/>
       <c r="B19" s="4" t="s">
         <v>181</v>
@@ -5772,7 +5833,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A20" s="6"/>
       <c r="B20" s="7" t="s">
         <v>184</v>
@@ -5793,7 +5854,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A21" s="5"/>
       <c r="B21" s="4" t="s">
         <v>282</v>
@@ -5814,7 +5875,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A22" s="6"/>
       <c r="B22" s="7" t="s">
         <v>235</v>
@@ -5835,7 +5896,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A23" s="5"/>
       <c r="B23" s="4" t="s">
         <v>285</v>
@@ -5856,7 +5917,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="24" spans="1:7">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A24" s="6"/>
       <c r="B24" s="7" t="s">
         <v>288</v>
@@ -5877,7 +5938,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="25" spans="1:7">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A25" s="5"/>
       <c r="B25" s="4" t="s">
         <v>291</v>
@@ -5898,7 +5959,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A26" s="6"/>
       <c r="B26" s="7" t="s">
         <v>294</v>
@@ -5919,7 +5980,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="27" spans="1:7">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A27" s="5"/>
       <c r="B27" s="4" t="s">
         <v>213</v>
@@ -5940,7 +6001,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A28" s="6"/>
       <c r="B28" s="7" t="s">
         <v>220</v>
@@ -5961,7 +6022,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A29" s="5"/>
       <c r="B29" s="4" t="s">
         <v>32</v>
@@ -5982,7 +6043,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A30" s="6"/>
       <c r="B30" s="7" t="s">
         <v>300</v>
@@ -6003,7 +6064,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A31" s="5"/>
       <c r="B31" s="4" t="s">
         <v>303</v>
@@ -6024,7 +6085,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="32" spans="1:7">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A32" s="5"/>
       <c r="B32" s="5"/>
       <c r="C32" s="5"/>
@@ -6033,7 +6094,7 @@
       <c r="F32" s="5"/>
       <c r="G32" s="5"/>
     </row>
-    <row r="33" spans="1:7">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A33" s="5"/>
       <c r="B33" s="5"/>
       <c r="C33" s="5"/>
@@ -6042,7 +6103,7 @@
       <c r="F33" s="5"/>
       <c r="G33" s="5"/>
     </row>
-    <row r="34" spans="1:7" ht="28.5" customHeight="1">
+    <row r="34" spans="1:7" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A34" s="5"/>
       <c r="B34" s="5"/>
       <c r="C34" s="5"/>
@@ -6060,7 +6121,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:G34"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="2" width="26" customWidth="1"/>
@@ -6071,7 +6132,7 @@
     <col min="7" max="7" width="50" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="20.100000000000001" customHeight="1">
+    <row r="1" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -6094,7 +6155,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A2" s="3" t="s">
         <v>306</v>
       </c>
@@ -6117,7 +6178,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A3" s="5"/>
       <c r="B3" s="4" t="s">
         <v>308</v>
@@ -6138,7 +6199,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A4" s="6"/>
       <c r="B4" s="7" t="s">
         <v>311</v>
@@ -6159,7 +6220,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A5" s="5"/>
       <c r="B5" s="14" t="s">
         <v>314</v>
@@ -6180,7 +6241,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A6" s="6"/>
       <c r="B6" s="7" t="s">
         <v>74</v>
@@ -6201,7 +6262,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A7" s="5"/>
       <c r="B7" s="4" t="s">
         <v>32</v>
@@ -6222,7 +6283,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A8" s="6"/>
       <c r="B8" s="7" t="s">
         <v>319</v>
@@ -6243,7 +6304,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A9" s="5"/>
       <c r="B9" s="4" t="s">
         <v>322</v>
@@ -6264,7 +6325,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A10" s="6"/>
       <c r="B10" s="7" t="s">
         <v>325</v>
@@ -6285,7 +6346,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A11" s="5"/>
       <c r="B11" s="4" t="s">
         <v>36</v>
@@ -6306,7 +6367,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A12" s="6"/>
       <c r="B12" s="7" t="s">
         <v>39</v>
@@ -6327,7 +6388,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A13" s="5"/>
       <c r="B13" s="4" t="s">
         <v>43</v>
@@ -6348,7 +6409,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A14" s="5"/>
       <c r="B14" s="5"/>
       <c r="C14" s="5"/>
@@ -6357,7 +6418,7 @@
       <c r="F14" s="5"/>
       <c r="G14" s="5"/>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A15" s="3" t="s">
         <v>330</v>
       </c>
@@ -6380,7 +6441,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A16" s="5"/>
       <c r="B16" s="4" t="s">
         <v>138</v>
@@ -6401,7 +6462,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A17" s="6"/>
       <c r="B17" s="7" t="s">
         <v>334</v>
@@ -6422,7 +6483,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A18" s="5"/>
       <c r="B18" s="4" t="s">
         <v>337</v>
@@ -6443,7 +6504,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A19" s="6"/>
       <c r="B19" s="7" t="s">
         <v>339</v>
@@ -6464,7 +6525,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A20" s="5"/>
       <c r="B20" s="4" t="s">
         <v>342</v>
@@ -6485,7 +6546,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A21" s="6"/>
       <c r="B21" s="7" t="s">
         <v>344</v>
@@ -6506,7 +6567,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A22" s="5"/>
       <c r="B22" s="4" t="s">
         <v>147</v>
@@ -6527,7 +6588,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A23" s="5"/>
       <c r="B23" s="5"/>
       <c r="C23" s="5"/>
@@ -6536,7 +6597,7 @@
       <c r="F23" s="5"/>
       <c r="G23" s="5"/>
     </row>
-    <row r="24" spans="1:7">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A24" s="3" t="s">
         <v>347</v>
       </c>
@@ -6559,7 +6620,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="25" spans="1:7">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A25" s="5"/>
       <c r="B25" s="4" t="s">
         <v>138</v>
@@ -6580,7 +6641,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A26" s="6"/>
       <c r="B26" s="7" t="s">
         <v>352</v>
@@ -6601,7 +6662,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="27" spans="1:7">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A27" s="5"/>
       <c r="B27" s="4" t="s">
         <v>334</v>
@@ -6622,7 +6683,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A28" s="6"/>
       <c r="B28" s="7" t="s">
         <v>337</v>
@@ -6643,7 +6704,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A29" s="5"/>
       <c r="B29" s="4" t="s">
         <v>32</v>
@@ -6664,7 +6725,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A30" s="6"/>
       <c r="B30" s="7" t="s">
         <v>357</v>
@@ -6685,7 +6746,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A31" s="5"/>
       <c r="B31" s="4" t="s">
         <v>360</v>
@@ -6706,7 +6767,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="32" spans="1:7">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A32" s="5"/>
       <c r="B32" s="5"/>
       <c r="C32" s="5"/>
@@ -6715,7 +6776,7 @@
       <c r="F32" s="5"/>
       <c r="G32" s="5"/>
     </row>
-    <row r="33" spans="1:7">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A33" s="5"/>
       <c r="B33" s="5"/>
       <c r="C33" s="5"/>
@@ -6724,7 +6785,7 @@
       <c r="F33" s="5"/>
       <c r="G33" s="5"/>
     </row>
-    <row r="34" spans="1:7">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A34" s="5"/>
       <c r="B34" s="5"/>
       <c r="C34" s="5"/>
@@ -6741,7 +6802,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:F55"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="36" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
@@ -6751,7 +6812,7 @@
     <col min="6" max="6" width="50" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A1" s="2" t="s">
         <v>363</v>
       </c>
@@ -6771,7 +6832,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A2" s="8" t="s">
         <v>47</v>
       </c>
@@ -6791,7 +6852,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A3" s="8" t="s">
         <v>47</v>
       </c>
@@ -6811,7 +6872,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A4" s="8" t="s">
         <v>47</v>
       </c>
@@ -6831,7 +6892,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A5" s="8"/>
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
@@ -6839,7 +6900,7 @@
       <c r="E5" s="9"/>
       <c r="F5" s="9"/>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A6" s="8" t="s">
         <v>114</v>
       </c>
@@ -6859,7 +6920,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A7" s="8" t="s">
         <v>377</v>
       </c>
@@ -6879,7 +6940,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A8" s="8" t="s">
         <v>379</v>
       </c>
@@ -6899,7 +6960,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A9" s="8" t="s">
         <v>379</v>
       </c>
@@ -6919,7 +6980,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A10" s="8" t="s">
         <v>382</v>
       </c>
@@ -6939,7 +7000,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A11" s="8" t="s">
         <v>382</v>
       </c>
@@ -6959,7 +7020,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A12" s="8" t="s">
         <v>385</v>
       </c>
@@ -6979,7 +7040,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A13" s="8"/>
       <c r="B13" s="8"/>
       <c r="C13" s="8"/>
@@ -6987,7 +7048,7 @@
       <c r="E13" s="9"/>
       <c r="F13" s="9"/>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A14" s="8" t="s">
         <v>387</v>
       </c>
@@ -7007,7 +7068,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" spans="1:6" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A15" s="8" t="s">
         <v>114</v>
       </c>
@@ -7027,7 +7088,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="16" spans="1:6">
+    <row r="16" spans="1:6" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A16" s="8" t="s">
         <v>114</v>
       </c>
@@ -7047,7 +7108,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A17" s="8"/>
       <c r="B17" s="8"/>
       <c r="C17" s="8"/>
@@ -7055,7 +7116,7 @@
       <c r="E17" s="9"/>
       <c r="F17" s="9"/>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A18" s="8" t="s">
         <v>233</v>
       </c>
@@ -7075,7 +7136,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="19" spans="1:6">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A19" s="8" t="s">
         <v>278</v>
       </c>
@@ -7095,7 +7156,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A20" s="8" t="s">
         <v>278</v>
       </c>
@@ -7115,7 +7176,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A21" s="8" t="s">
         <v>278</v>
       </c>
@@ -7135,7 +7196,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="22" spans="1:6">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A22" s="8"/>
       <c r="B22" s="8"/>
       <c r="C22" s="8"/>
@@ -7143,7 +7204,7 @@
       <c r="E22" s="9"/>
       <c r="F22" s="9"/>
     </row>
-    <row r="23" spans="1:6">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A23" s="8" t="s">
         <v>387</v>
       </c>
@@ -7163,7 +7224,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="24" spans="1:6">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A24" s="8" t="s">
         <v>387</v>
       </c>
@@ -7183,7 +7244,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="25" spans="1:6">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A25" s="8" t="s">
         <v>387</v>
       </c>
@@ -7203,7 +7264,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="26" spans="1:6">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A26" s="8" t="s">
         <v>387</v>
       </c>
@@ -7223,7 +7284,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="27" spans="1:6">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A27" s="8"/>
       <c r="B27" s="8"/>
       <c r="C27" s="8"/>
@@ -7231,7 +7292,7 @@
       <c r="E27" s="9"/>
       <c r="F27" s="9"/>
     </row>
-    <row r="28" spans="1:6">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A28" s="8" t="s">
         <v>401</v>
       </c>
@@ -7251,7 +7312,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="29" spans="1:6">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A29" s="8" t="s">
         <v>401</v>
       </c>
@@ -7271,7 +7332,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="30" spans="1:6">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A30" s="8" t="s">
         <v>405</v>
       </c>
@@ -7291,7 +7352,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="31" spans="1:6">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A31" s="8"/>
       <c r="B31" s="8"/>
       <c r="C31" s="8"/>
@@ -7299,7 +7360,7 @@
       <c r="E31" s="9"/>
       <c r="F31" s="9"/>
     </row>
-    <row r="32" spans="1:6">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A32" s="8"/>
       <c r="B32" s="8"/>
       <c r="C32" s="8"/>
@@ -7307,7 +7368,7 @@
       <c r="E32" s="9"/>
       <c r="F32" s="9"/>
     </row>
-    <row r="33" spans="1:6">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A33" s="8"/>
       <c r="B33" s="8"/>
       <c r="C33" s="8"/>
@@ -7315,7 +7376,7 @@
       <c r="E33" s="9"/>
       <c r="F33" s="9"/>
     </row>
-    <row r="34" spans="1:6">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A34" s="8"/>
       <c r="B34" s="8"/>
       <c r="C34" s="8"/>
@@ -7323,7 +7384,7 @@
       <c r="E34" s="9"/>
       <c r="F34" s="9"/>
     </row>
-    <row r="35" spans="1:6">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A35" s="8"/>
       <c r="B35" s="8"/>
       <c r="C35" s="8"/>
@@ -7331,7 +7392,7 @@
       <c r="E35" s="9"/>
       <c r="F35" s="9"/>
     </row>
-    <row r="36" spans="1:6">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A36" s="8"/>
       <c r="B36" s="8"/>
       <c r="C36" s="8"/>
@@ -7339,7 +7400,7 @@
       <c r="E36" s="9"/>
       <c r="F36" s="9"/>
     </row>
-    <row r="37" spans="1:6">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A37" s="8"/>
       <c r="B37" s="8"/>
       <c r="C37" s="8"/>
@@ -7347,7 +7408,7 @@
       <c r="E37" s="9"/>
       <c r="F37" s="9"/>
     </row>
-    <row r="38" spans="1:6">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A38" s="8"/>
       <c r="B38" s="8"/>
       <c r="C38" s="8"/>
@@ -7355,7 +7416,7 @@
       <c r="E38" s="9"/>
       <c r="F38" s="9"/>
     </row>
-    <row r="39" spans="1:6">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A39" s="8"/>
       <c r="B39" s="8"/>
       <c r="C39" s="8"/>
@@ -7363,7 +7424,7 @@
       <c r="E39" s="9"/>
       <c r="F39" s="9"/>
     </row>
-    <row r="41" spans="1:6">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A41" s="8"/>
       <c r="B41" s="8"/>
       <c r="C41" s="8"/>
@@ -7371,7 +7432,7 @@
       <c r="E41" s="9"/>
       <c r="F41" s="9"/>
     </row>
-    <row r="42" spans="1:6">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A42" s="8"/>
       <c r="B42" s="8"/>
       <c r="C42" s="8"/>
@@ -7379,7 +7440,7 @@
       <c r="E42" s="9"/>
       <c r="F42" s="9"/>
     </row>
-    <row r="43" spans="1:6">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A43" s="8"/>
       <c r="B43" s="8"/>
       <c r="C43" s="8"/>
@@ -7387,7 +7448,7 @@
       <c r="E43" s="9"/>
       <c r="F43" s="9"/>
     </row>
-    <row r="44" spans="1:6">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A44" s="8"/>
       <c r="B44" s="8"/>
       <c r="C44" s="8"/>
@@ -7395,7 +7456,7 @@
       <c r="E44" s="9"/>
       <c r="F44" s="9"/>
     </row>
-    <row r="45" spans="1:6">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A45" s="8"/>
       <c r="B45" s="8"/>
       <c r="C45" s="8"/>
@@ -7403,7 +7464,7 @@
       <c r="E45" s="9"/>
       <c r="F45" s="9"/>
     </row>
-    <row r="46" spans="1:6">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A46" s="8"/>
       <c r="B46" s="8"/>
       <c r="C46" s="8"/>
@@ -7411,7 +7472,7 @@
       <c r="E46" s="9"/>
       <c r="F46" s="9"/>
     </row>
-    <row r="48" spans="1:6">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A48" s="8"/>
       <c r="B48" s="8"/>
       <c r="C48" s="8"/>
@@ -7419,7 +7480,7 @@
       <c r="E48" s="9"/>
       <c r="F48" s="9"/>
     </row>
-    <row r="49" spans="1:6">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A49" s="8"/>
       <c r="B49" s="8"/>
       <c r="C49" s="8"/>
@@ -7427,7 +7488,7 @@
       <c r="E49" s="9"/>
       <c r="F49" s="9"/>
     </row>
-    <row r="50" spans="1:6">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A50" s="8"/>
       <c r="B50" s="8"/>
       <c r="C50" s="8"/>
@@ -7435,7 +7496,7 @@
       <c r="E50" s="9"/>
       <c r="F50" s="9"/>
     </row>
-    <row r="51" spans="1:6">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A51" s="8"/>
       <c r="B51" s="8"/>
       <c r="C51" s="8"/>
@@ -7443,7 +7504,7 @@
       <c r="E51" s="9"/>
       <c r="F51" s="9"/>
     </row>
-    <row r="53" spans="1:6">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A53" s="8"/>
       <c r="B53" s="8"/>
       <c r="C53" s="8"/>
@@ -7451,7 +7512,7 @@
       <c r="E53" s="9"/>
       <c r="F53" s="9"/>
     </row>
-    <row r="54" spans="1:6">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A54" s="8"/>
       <c r="B54" s="8"/>
       <c r="C54" s="8"/>
@@ -7459,7 +7520,7 @@
       <c r="E54" s="9"/>
       <c r="F54" s="9"/>
     </row>
-    <row r="55" spans="1:6">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A55" s="8"/>
       <c r="B55" s="8"/>
       <c r="C55" s="8"/>
@@ -7476,13 +7537,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:B16"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="161.42578125" customWidth="1"/>
+    <col min="2" max="2" width="161.3984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A1" s="13" t="s">
         <v>407</v>
       </c>
@@ -7490,7 +7551,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="21" customHeight="1">
+    <row r="2" spans="1:2" ht="21" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" s="11" t="s">
         <v>409</v>
       </c>
@@ -7498,7 +7559,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="30.75">
+    <row r="3" spans="1:2" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A3" s="12" t="s">
         <v>411</v>
       </c>
@@ -7506,7 +7567,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A4" s="11" t="s">
         <v>413</v>
       </c>
@@ -7514,7 +7575,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="30.75">
+    <row r="5" spans="1:2" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A5" s="12" t="s">
         <v>415</v>
       </c>
@@ -7522,7 +7583,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A6" s="11" t="s">
         <v>417</v>
       </c>
@@ -7530,7 +7591,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="22.5" customHeight="1">
+    <row r="7" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A7" s="12" t="s">
         <v>419</v>
       </c>
@@ -7538,7 +7599,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="22.5" customHeight="1">
+    <row r="8" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A8" s="11" t="s">
         <v>421</v>
       </c>
@@ -7546,7 +7607,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="30.75">
+    <row r="9" spans="1:2" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A9" s="12" t="s">
         <v>423</v>
       </c>
@@ -7554,7 +7615,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="21.75" customHeight="1">
+    <row r="10" spans="1:2" ht="21.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A10" s="11" t="s">
         <v>425</v>
       </c>
@@ -7562,7 +7623,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="26.25" customHeight="1">
+    <row r="11" spans="1:2" ht="26.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A11" s="12" t="s">
         <v>427</v>
       </c>
@@ -7570,7 +7631,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="31.5" customHeight="1">
+    <row r="12" spans="1:2" ht="31.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A12" s="11" t="s">
         <v>429</v>
       </c>
@@ -7578,19 +7639,19 @@
         <v>430</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A13" s="12"/>
       <c r="B13" s="5"/>
     </row>
-    <row r="14" spans="1:2">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A14" s="11"/>
       <c r="B14" s="6"/>
     </row>
-    <row r="15" spans="1:2">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A15" s="12"/>
       <c r="B15" s="5"/>
     </row>
-    <row r="16" spans="1:2">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A16" s="10"/>
       <c r="B16" s="9"/>
     </row>
